--- a/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T08:52:52+00:00</t>
+    <t>2024-10-25T07:50:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
+++ b/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDCoverageEligibilityRequest.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:50:17+00:00</t>
+    <t>2024-10-29T09:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -467,13 +467,13 @@
     <t>"Verlaengerungstage:"Anzahl der Verlaengerungstage bei Verlaengerung.</t>
   </si>
   <si>
-    <t>CoverageEligibilityRequest.extension:premiumKlasse</t>
-  </si>
-  <si>
-    <t>premiumKlasse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-premiumClass}
+    <t>CoverageEligibilityRequest.extension:sonderklasse</t>
+  </si>
+  <si>
+    <t>sonderklasse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-sonderklasse}
 </t>
   </si>
   <si>
